--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.105.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.105.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.105" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.105" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.105.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.105.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0105.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0105.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -815,7 +815,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.105.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.105.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.105" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.105" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y18"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="51" customWidth="1" min="14" max="14"/>
-    <col width="35" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -609,22 +609,30 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: (41)ã€‚</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | symbol-only separator/garbage line :: (41)。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: THE MASTERâ€™S OFFICE.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]98</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]98</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 98</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr"/>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]98</t>
+        </is>
+      </c>
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr"/>
@@ -649,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -660,7 +668,7 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L95: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: (41)ã€‚</t>
+          <t>L95: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | symbol-only separator/garbage line :: (41)。</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr"/>
@@ -668,7 +676,7 @@
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L13: symbol-only separator/garbage line :: (20).</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | symbol-only separator/garbage line :: (41)。</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr"/>
@@ -705,13 +713,17 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr"/>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>L234: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
       <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L30: symbol-only separator/garbage line :: (30).</t>
+          <t>L13: symbol-only separator/garbage line :: (20).</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr"/>
@@ -734,7 +746,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -754,7 +766,7 @@
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L40: symbol-only separator/garbage line :: (39).</t>
+          <t>L30: symbol-only separator/garbage line :: (30).</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr"/>
@@ -797,7 +809,7 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L56: symbol-only separator/garbage line :: (49).</t>
+          <t>L40: symbol-only separator/garbage line :: (39).</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr"/>
@@ -840,7 +852,7 @@
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L65: symbol-only separator/garbage line :: (50).</t>
+          <t>L56: symbol-only separator/garbage line :: (49).</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr"/>
@@ -883,7 +895,7 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L76: symbol-only separator/garbage line :: (59).</t>
+          <t>L65: symbol-only separator/garbage line :: (50).</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr"/>
@@ -926,7 +938,7 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L85: symbol-only separator/garbage line :: (37).</t>
+          <t>L76: symbol-only separator/garbage line :: (59).</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr"/>
@@ -949,7 +961,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -969,7 +981,7 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L93: isolated marker/symbol line :: 98</t>
+          <t>L85: symbol-only separator/garbage line :: (37).</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr"/>
@@ -997,7 +1009,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1012,7 +1024,7 @@
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L111: symbol-only separator/garbage line :: (20).</t>
+          <t>L93: isolated marker/symbol line :: 98</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr"/>
@@ -1035,12 +1047,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1055,7 +1067,7 @@
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L125: isolated marker/symbol line :: 4</t>
+          <t>L95: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | symbol-only separator/garbage line :: (41)。</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr"/>
@@ -1098,7 +1110,7 @@
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L139: symbol-only separator/garbage line :: (30).</t>
+          <t>L111: symbol-only separator/garbage line :: (20).</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr"/>
@@ -1141,7 +1153,7 @@
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L155: symbol-only separator/garbage line :: (39).</t>
+          <t>L125: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr"/>
@@ -1184,7 +1196,7 @@
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L180: symbol-only separator/garbage line :: (49).</t>
+          <t>L139: symbol-only separator/garbage line :: (30).</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr"/>
@@ -1227,7 +1239,7 @@
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L193: symbol-only separator/garbage line :: (50).</t>
+          <t>L155: symbol-only separator/garbage line :: (39).</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr"/>
@@ -1270,7 +1282,7 @@
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L209: symbol-only separator/garbage line :: (59).</t>
+          <t>L180: symbol-only separator/garbage line :: (49).</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr"/>
@@ -1301,7 +1313,7 @@
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L223: symbol-only separator/garbage line :: (37).</t>
+          <t>L193: symbol-only separator/garbage line :: (50).</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr"/>
@@ -1316,6 +1328,99 @@
       <c r="X18" s="1" t="inlineStr"/>
       <c r="Y18" s="1" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr"/>
+      <c r="B19" s="1" t="inlineStr"/>
+      <c r="C19" s="1" t="inlineStr"/>
+      <c r="D19" s="1" t="inlineStr"/>
+      <c r="E19" s="1" t="inlineStr"/>
+      <c r="F19" s="1" t="inlineStr"/>
+      <c r="G19" s="1" t="inlineStr"/>
+      <c r="H19" s="1" t="inlineStr"/>
+      <c r="I19" s="1" t="inlineStr"/>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr"/>
+      <c r="L19" s="1" t="inlineStr"/>
+      <c r="M19" s="1" t="inlineStr"/>
+      <c r="N19" s="1" t="inlineStr">
+        <is>
+          <t>L209: symbol-only separator/garbage line :: (59).</t>
+        </is>
+      </c>
+      <c r="O19" s="1" t="inlineStr"/>
+      <c r="P19" s="1" t="inlineStr"/>
+      <c r="Q19" s="1" t="inlineStr"/>
+      <c r="R19" s="1" t="inlineStr"/>
+      <c r="S19" s="1" t="inlineStr"/>
+      <c r="T19" s="1" t="inlineStr"/>
+      <c r="U19" s="1" t="inlineStr"/>
+      <c r="V19" s="1" t="inlineStr"/>
+      <c r="W19" s="1" t="inlineStr"/>
+      <c r="X19" s="1" t="inlineStr"/>
+      <c r="Y19" s="1" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr"/>
+      <c r="B20" s="1" t="inlineStr"/>
+      <c r="C20" s="1" t="inlineStr"/>
+      <c r="D20" s="1" t="inlineStr"/>
+      <c r="E20" s="1" t="inlineStr"/>
+      <c r="F20" s="1" t="inlineStr"/>
+      <c r="G20" s="1" t="inlineStr"/>
+      <c r="H20" s="1" t="inlineStr"/>
+      <c r="I20" s="1" t="inlineStr"/>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
+      <c r="L20" s="1" t="inlineStr"/>
+      <c r="M20" s="1" t="inlineStr"/>
+      <c r="N20" s="1" t="inlineStr">
+        <is>
+          <t>L223: symbol-only separator/garbage line :: (37).</t>
+        </is>
+      </c>
+      <c r="O20" s="1" t="inlineStr"/>
+      <c r="P20" s="1" t="inlineStr"/>
+      <c r="Q20" s="1" t="inlineStr"/>
+      <c r="R20" s="1" t="inlineStr"/>
+      <c r="S20" s="1" t="inlineStr"/>
+      <c r="T20" s="1" t="inlineStr"/>
+      <c r="U20" s="1" t="inlineStr"/>
+      <c r="V20" s="1" t="inlineStr"/>
+      <c r="W20" s="1" t="inlineStr"/>
+      <c r="X20" s="1" t="inlineStr"/>
+      <c r="Y20" s="1" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr"/>
+      <c r="B21" s="1" t="inlineStr"/>
+      <c r="C21" s="1" t="inlineStr"/>
+      <c r="D21" s="1" t="inlineStr"/>
+      <c r="E21" s="1" t="inlineStr"/>
+      <c r="F21" s="1" t="inlineStr"/>
+      <c r="G21" s="1" t="inlineStr"/>
+      <c r="H21" s="1" t="inlineStr"/>
+      <c r="I21" s="1" t="inlineStr"/>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr"/>
+      <c r="L21" s="1" t="inlineStr"/>
+      <c r="M21" s="1" t="inlineStr"/>
+      <c r="N21" s="1" t="inlineStr">
+        <is>
+          <t>L234: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="O21" s="1" t="inlineStr"/>
+      <c r="P21" s="1" t="inlineStr"/>
+      <c r="Q21" s="1" t="inlineStr"/>
+      <c r="R21" s="1" t="inlineStr"/>
+      <c r="S21" s="1" t="inlineStr"/>
+      <c r="T21" s="1" t="inlineStr"/>
+      <c r="U21" s="1" t="inlineStr"/>
+      <c r="V21" s="1" t="inlineStr"/>
+      <c r="W21" s="1" t="inlineStr"/>
+      <c r="X21" s="1" t="inlineStr"/>
+      <c r="Y21" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
